--- a/Files/download.xlsx
+++ b/Files/download.xlsx
@@ -445,7 +445,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/Files/download.xlsx
+++ b/Files/download.xlsx
@@ -445,6 +445,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
+  <sheetFormatPr customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
